--- a/public/report.xlsx
+++ b/public/report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Projects\go-report\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF146209-D788-4BAE-9552-7E2171C5B99E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB6F0FBA-7FB0-4298-B74C-BC2299F8924D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5B6F2779-D823-4A57-9B01-1219A08945D4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>TANGGAL</t>
   </si>
@@ -89,67 +89,13 @@
     <t>RITASE</t>
   </si>
   <si>
-    <t>DBGX26041201307</t>
-  </si>
-  <si>
-    <t>DKGX26041201267</t>
-  </si>
-  <si>
-    <t>DBGX26041201306</t>
-  </si>
-  <si>
-    <t>DBGX26041201269</t>
-  </si>
-  <si>
-    <t>DBGX26041201497</t>
-  </si>
-  <si>
-    <t>DBGX26041301115</t>
-  </si>
-  <si>
-    <t>DBGX26041301394</t>
-  </si>
-  <si>
-    <t>DBGX26041301120</t>
-  </si>
-  <si>
-    <t>DBGX26041301346</t>
-  </si>
-  <si>
-    <t>DKGX26041301502</t>
-  </si>
-  <si>
-    <t>DBGX26041301217</t>
-  </si>
-  <si>
-    <t>DKGX26041301139</t>
-  </si>
-  <si>
-    <t>DBGX26041301166</t>
-  </si>
-  <si>
-    <t>DBGX26041301196</t>
-  </si>
-  <si>
-    <t>DBGX26041301285</t>
-  </si>
-  <si>
-    <t>DKGX26041301251</t>
-  </si>
-  <si>
-    <t>DBGX26041301377</t>
-  </si>
-  <si>
-    <t>DBGX26041301197</t>
-  </si>
-  <si>
-    <t>DBGX26041301195</t>
-  </si>
-  <si>
-    <t>DBGX26041301528</t>
-  </si>
-  <si>
-    <t>DBGX26041301144</t>
+    <t xml:space="preserve"> JBGX26041500101 </t>
+  </si>
+  <si>
+    <t>JBGX26041500106</t>
+  </si>
+  <si>
+    <t>JBGX26041500108</t>
   </si>
 </sst>
 </file>
@@ -528,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4EE7CFF-E402-495A-BAD5-5EA167CD3DC0}">
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
@@ -614,96 +560,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C12" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C15" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C17" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C19" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C20" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C21" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C22" t="s">
-        <v>37</v>
-      </c>
-    </row>
+    <row r="12" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
